--- a/SMS_Consolidated_Report.xlsx
+++ b/SMS_Consolidated_Report.xlsx
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report Generated: 06 May 2026, 09:36 PM</t>
+          <t>Report Generated: 06 May 2026, 10:20 PM</t>
         </is>
       </c>
     </row>
